--- a/data-src/약대기준.xlsx
+++ b/data-src/약대기준.xlsx
@@ -153,7 +153,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>수능 과학탐구 2과목 응시자 입니까?</t>
+    <t>수능 탐구 과목은 어떻게 응시합니까?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -165,7 +165,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1. 네  2. 아니오</t>
+    <t>1. 과탐 2과목  2. 과탐 1과목 + 사탐 1과목  3. 사탐 2과목</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1326,43 +1326,43 @@
         <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
